--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Solutions Architect (Financial Services)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Glue, SQS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd7a8d512b43154</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data/Analytics Engineer</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Heluna Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
+          <t>https://www.indeed.com/viewjob?jk=53d5f21773f04216</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Data/Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Heluna Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Advisor Software Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4914e8c40e18d9</t>
+          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cloud solution engineer</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data engineer</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Kafka, Kafka Connect, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3caee5240d78</t>
+          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>cloud solution engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Azure Databricks Admin</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Databricks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
+          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Data Solutions Engineer - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, GCP, Spark</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008ddae8bcb982b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42117b5a31b019c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior MS Fabric Data Engineer - Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Architect – R01566974</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Senior MS Fabric Data Engineer - Azure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Architect – R01566974</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer III</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Software Engineer AI/ML Ops</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
+          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
+          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
+          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
+          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
+          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
+          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
+          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
+          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
+          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
+          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
+          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
+          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
+          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
+          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
+          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
+          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
+          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada, KY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
+          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Canada, KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Solutions Software Developer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AtkinsRéalis</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6623209a0f6f745a</t>
+          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kenneth Copeland Ministries</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Newark, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Kenneth Copeland Ministries</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Oracle Human Capital Management Analyst</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JBI Software</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Oracle Human Capital Management Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FocusPointSAP</t>
+          <t>JBI Software</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,42 +3951,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, GitHub Actions, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64c9105e7675d73</t>
+          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,59 +3996,59 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3768e1a09d9081</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03c61711e39cecb</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5c30ca545147b0</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e3324089b2ba14</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>AI Engineer – Financial Services Hybrid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>RiskSpan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RiskSpan</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Bharathvio Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Kent, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior OpenTelemetry Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior OpenTelemetry Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Financial Data Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, ETL, Tableau, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56390aee6504595</t>
+          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
+          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbcc02e72366f37a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,120 +4756,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf99ed11d3323d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>cloud solution engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
+          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cloud solution engineer</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[P] Data Engineer, Safeguards</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Databricks Admin</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30458fe3d780cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Data Solutions Engineer - Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Databricks</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
@@ -1343,25 +1343,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior MS Fabric Data Engineer - Azure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Architect – R01566974</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f069643153aaaa93</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior MS Fabric Data Engineer - Azure</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Architect – R01566974</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a8b4ddc2c212a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer III</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML Ops</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817383301a886adf</t>
+          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
+          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
+          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
+          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
+          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
+          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
+          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
+          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
+          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
+          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
+          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
+          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
+          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
+          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
+          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
+          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
+          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Canada, KY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Canada, KY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Kenneth Copeland Ministries</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newark, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Oracle, SQL Server, NoSQL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749f3eb9090b4ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle Human Capital Management Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>JBI Software</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kenneth Copeland Ministries</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Newark, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Oracle Human Capital Management Analyst</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JBI Software</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,59 +3996,59 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712497bf338832f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>AI Engineer – Financial Services Hybrid</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>RiskSpan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bectran Inc</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Bharathvio Technologies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Kent, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Snowflake DBT Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25f819418a170c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RiskSpan</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior OpenTelemetry Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,260 +4511,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, GCP, Kafka, ELT, AKS, CloudWatch</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcdf51b6ddf79c84</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>V4C.ai</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bff5e93f15d9f562</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cloud solution engineer</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0262593736bdcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[P] Data Engineer, Safeguards</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Data Solutions Engineer - Databricks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Databricks</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Architect – R01566974</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Architect – R01566974</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c855924cfe57ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Kenneth Copeland Ministries</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kenneth Copeland Ministries</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Newark, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Oracle Human Capital Management Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>JBI Software</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Oracle Human Capital Management Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JBI Software</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
+          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bectran Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>AI Engineer – Financial Services Hybrid</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>RiskSpan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RiskSpan</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Bharathvio Technologies</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Kent, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,52 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
+          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Advisor Software Engineer (AI/ML)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=580224382e8a12e0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Advisor Software Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
+          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[P] Data Engineer, Safeguards</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
+          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>Khoj Information Technology, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Nlineaxis It Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
+          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Databricks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
+          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Sr Data Science Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Data Solutions Engineer - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer, Training Transformation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Java Full Stack Developer (Senior)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior MS Fabric Data Engineer - Azure</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Architect – R01566974</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Senior MS Fabric Data Engineer - Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Calypso Technical Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Architect – R01566974</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer III</t>
+          <t>Business Application Developer - Fullstack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f46ca1a397036c7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
+          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
+          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
+          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
+          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
+          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
+          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
+          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
+          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
+          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
+          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
+          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
+          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
+          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
+          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
+          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
+          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f334fbdcdef23c84</t>
+          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, RDS, Scala, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce82a6c8b0ad6bef</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kenneth Copeland Ministries</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newark, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,59 +3716,59 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Oracle Human Capital Management Analyst</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JBI Software</t>
+          <t>Kenneth Copeland Ministries</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Oracle Human Capital Management Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JBI Software</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,42 +3846,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bectran Inc</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RiskSpan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,42 +4161,42 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI App Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>Clackamas, OR, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Engineer – Financial Services Hybrid</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>RiskSpan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Databricks Lakehouse, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf3c7bdde5b4d60</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Bharathvio Technologies</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Kent, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
+          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,15 +4476,120 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
         </is>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Customer Data Products)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Redshift, Step Functions, RDS, Hadoop, Hive, MapReduce, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd7a8d512b43154</t>
+          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, SQS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d5f21773f04216</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd7a8d512b43154</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Solutions Architect (Financial Services)</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
+          <t>https://www.indeed.com/viewjob?jk=53d5f21773f04216</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data/Analytics Engineer</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Heluna Health</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0b7cd5c47cd65a</t>
+          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Advisor Software Engineer (AI/ML)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Dorleco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
         </is>
       </c>
     </row>
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Advisor Software Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
+          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Cloud Data Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
+          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MongoDB Architect (SQL to MongoDB Migration Specialist)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Khoj Information Technology, Inc.</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1fd822e8cfcad0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[P] Data Engineer, Safeguards</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
+          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nlineaxis It Solutions</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>Nlineaxis It Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Platform automation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1440a2d2356cbc69</t>
+          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Science Engineer</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580347ece6eeeb68</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Training Transformation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2acffa5291128c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea57d1c34ac586d9</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer (Senior)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d0e2593357ebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior MS Fabric Data Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Calypso Technical Engineer</t>
+          <t>Senior MS Fabric Data Engineer - Azure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Architect – R01566974</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2571b229b6c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Senior Calypso Technical Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Application Developer - Fullstack</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,69 +1746,69 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3fc8579b2391c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
+          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
+          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
+          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
+          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
+          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
+          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
+          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
+          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
+          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
+          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
+          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
+          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
+          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
+          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
+          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
+          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
+          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
+          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
+          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
+          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
+          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aa6109dc953b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, RDS, Scala, Kafka, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce82a6c8b0ad6bef</t>
+          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, RDS, Scala, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+          <t>https://www.indeed.com/viewjob?jk=ce82a6c8b0ad6bef</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kenneth Copeland Ministries</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Newark, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce92c0fbadcfe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Oracle Human Capital Management Analyst</t>
+          <t>Senior Solutions Architect - AI/ML - Services Delivery</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JBI Software</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2278e5694be1021c</t>
+          <t>https://www.indeed.com/viewjob?jk=1440e5e9f75e65a5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efc2581c2e7798d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, Power BI, Tableau, CI/CD, Kubernetes</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4348c2e52b6813</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Software Engineer - J2EE / Jenkins / Spring Boot</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ea107a3e8076230f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer</t>
+          <t>Full Stack Developer: Ai Enablement and Agentic Develoopment</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bectran Inc</t>
+          <t>Excellis Consulting Corporation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9aedd178e13717</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1988f00e94a6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI App Developer</t>
+          <t>AI Engineer – Financial Services Hybrid</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>RiskSpan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Clackamas, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197a4f7fe1f8f98</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RiskSpan</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Bharathvio Technologies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Kent, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
+          <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Security Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=0732962234af33bb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667f77c9d7a9c12e</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9629f01e9f1302a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Calypso Technical Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Senior Calypso Technical Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a84346c1964ec20</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate Software &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea249ca23dcb7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
         </is>
       </c>
     </row>
@@ -3693,55 +3693,55 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78d1198797715b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Senior Solutions Architect - AI/ML - Services Delivery</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=1440e5e9f75e65a5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - AI/ML - Services Delivery</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1440e5e9f75e65a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - J2EE / Jenkins / Spring Boot</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea107a3e8076230f</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Senior Software Engineer - J2EE / Jenkins / Spring Boot</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea107a3e8076230f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bectran Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Developer: Ai Enablement and Agentic Develoopment</t>
+          <t>AI Engineer – Financial Services Hybrid</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Excellis Consulting Corporation</t>
+          <t>RiskSpan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9aedd178e13717</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
+          <t>Data Engineer/Sr. BI Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RiskSpan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
+          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer/Sr. BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bharathvio Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kent, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, SQL Server, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a669b5372e08d533</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
+          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,122 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33652e6c92967b96</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Customer Data Products)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Barnes Aerospace</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Step Functions, RDS, Hadoop, Hive, MapReduce, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6c863fad4f5188</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Customer Data Products)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Redshift, Step Functions, RDS, Hadoop, Hive, MapReduce, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd7a8d512b43154</t>
+          <t>https://www.indeed.com/viewjob?jk=cce51fb4ed88355c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, SQS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d5f21773f04216</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd7a8d512b43154</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Architect (Financial Services)</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b839de2e42fa796c</t>
+          <t>https://www.indeed.com/viewjob?jk=53d5f21773f04216</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>Dorleco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580224382e8a12e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dorleco</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=580224382e8a12e0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Developer/Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9553c5cf6b0e55e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Advisor Software Engineer (AI/ML)</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9365b54c99b47a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Architect</t>
+          <t>Advisor Software Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=76ab24dd411e42cd</t>
         </is>
       </c>
     </row>
@@ -853,35 +853,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[P] Data Engineer, Safeguards</t>
+          <t>Cloud Data Platform Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
+          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>[P] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=baef6db4055ef653</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edba7e9ad21f7227</t>
+          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform automation Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Databricks, Kafka, Snowflake, dbt, Tableau</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42a5bdcf2411ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Databricks</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dda8e4da07c78b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea57d1c34ac586d9</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Security Engineer III - AI/ML</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732962234af33bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,137 +1406,137 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1c2968e4c859ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6be32f39256627</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dd8c61c6f7c9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3427cac673c0828</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior MS Fabric Data Engineer - Azure</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf586f663393905d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Calypso Technical Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,129 +1721,129 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Calypso Technical Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, RDS, Scala, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=ce82a6c8b0ad6bef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,172 +2001,172 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c62c4e7ce52816</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26df8ecfe6a67d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c27c0e013e3176</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c6fc067a14cd01</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Solutions Architect - AI/ML - Services Delivery</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ae43139e421015</t>
+          <t>https://www.indeed.com/viewjob?jk=1440e5e9f75e65a5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior AI Software Engineer, Product</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658083105be37fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b5b6c3a2a9b089</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,242 +2246,242 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff874c726c6d174b</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5f2c43370385dc</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Database Engineer (DBRE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d146448bc1ed6f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0ba045d78e688</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer - J2EE / Jenkins / Spring Boot</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dc41f3d1e6ef0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea107a3e8076230f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4bae38df86e03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a180a1e1ed21cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Bectran Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ddd7c43b55f71</t>
+          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42460f2d5d6c2dc2</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad8c4f4c77ffbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d0a5e82c1874b</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6a850caef1d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,102 +2666,102 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8123be1cb7ab6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64294d24071838</t>
+          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204e97c970316ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2770,1721 +2770,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fa88614b071867</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ffda87ddfb642b</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=047558f0baabe95a</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Jackson, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c9a818bf8a86c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Hope Hull, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7cc5edd8948ce9</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Kennesaw, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f38bf854652c94f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be842fb79d8cc443</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Fremont, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fd2a43ada3bc92</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Pawtucket, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce1ae8e7b69f496</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>New Franken, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d885cd296a96b39</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f2f9e0c1ec3263</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>UT, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e382d6d5ade69</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a054f6247f0af463</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Columbia, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d67e69c8f22631f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Okemos, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edc29795b2e72de2</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15b875d534cd3ea2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1f71919ce639a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Charleston, WV, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b39116b0df22731</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=011066a877bea2b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf9ba4924c8cbfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Upper Darby, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8da43a2a43902c</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23eb72012db7f8d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c983a104094bc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ac0b7f78a02869c</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=887cb24b5bd4709d</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr Product Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, RDS, Scala, Kafka, MySQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce82a6c8b0ad6bef</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Associate Software &amp; Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>LSEG (London Stock Exchange Group)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d27da61496d978</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>EXL Service</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer - GCP services</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>I8IS INC.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer - GCP services</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect - AI/ML - Services Delivery</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1440e5e9f75e65a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Oracle, ETL, REST API integration, CI/CD, Jenkins, Jenkins, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d1da01ac9b72b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior AI Software Engineer, Product</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>brightwheel</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Blue Orange Digital</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ImagineX Consulting</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Nationwide Mutual Insurance Company</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Cyber Security Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Bectran Inc</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Schaumburg, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - J2EE / Jenkins / Spring Boot</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea107a3e8076230f</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Snowflake Data Architect</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>SEI Investments Developments</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Oaks, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>AI Engineer – Financial Services Hybrid</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>RiskSpan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a74bffab03834</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Platform Engineer, Azure / DevOps</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Engineer/Sr. BI Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55e2a13c922c77db</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Alarm.com</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Lake Storage, Kafka, SQL Server, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f4cd7071264d74</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95fd730b43f96dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c115acdaa57dbce</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dorleco</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=580224382e8a12e0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>Dorleco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580224382e8a12e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2316c19c169e1b3</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Data Platform Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAVISHTY</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
+          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>SAVISHTY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5de4f159f9c510</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Architect</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Impala, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b49a29e977cbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b17a37638efda50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nlineaxis It Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
+          <t>https://www.indeed.com/viewjob?jk=c12624733c865304</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Snowflake/DataStage)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fuel Cycle</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Scala, Kafka, Snowflake, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
+          <t>https://www.indeed.com/viewjob?jk=13d171a250563755</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Nlineaxis It Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a907408dc33d66c2</t>
+          <t>https://www.indeed.com/viewjob?jk=bcac5ba7033fe638</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Fuel Cycle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Glue, Athena, S3, IAM, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621a2f404ef769bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74bc8a5c70207a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ac874b2ab78b1</t>
+          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Scala, Oracle, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fa7de8103bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>LaunchDarkly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Databricks, Scala, ETL, Power BI, CI/CD</t>
+          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b5a191541e3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Kab systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Career TEAM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905100aea4306c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1c2968e4c859ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6be32f39256627</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1c2968e4c859ad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6be32f39256627</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Calypso Technical Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8903d4fd47c4bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,137 +1721,137 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038e28e57828d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, RDS, Scala, Kafka, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce82a6c8b0ad6bef</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Engineer, BI - Onsite</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - AI/ML - Services Delivery</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, ETL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1440e5e9f75e65a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer, Product</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0e5fc443be597</t>
+          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (DBRE)</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - J2EE / Jenkins / Spring Boot</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea107a3e8076230f</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer</t>
+          <t>Senior Database Engineer (DBRE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bectran Inc</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git, CloudTrail</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55d6bf14862ee19</t>
+          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,15 +2761,190 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Platform Engineer, Azure / DevOps</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Genworth</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Hardware &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>oura</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Snowflake, Dimensional Modeling, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0c6767bdba48a7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Frontend Software Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>

--- a/results/job_matches_2026-07-02.xlsx
+++ b/results/job_matches_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Data Platform</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Kinesis, Redshift, Athena, Timestream, S3, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69cd71d265ff36ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89b3b31bb1d57b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Career TEAM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3070c24cd1abbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kab systems</t>
+          <t>Origami Risk LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb8ba4237e5aa54</t>
+          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Career TEAM</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759bc95f0f620a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Senior Application Development Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Origami Risk LLC</t>
+          <t>Idaho Power Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Databricks, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121742c1c0a0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Application Development Analyst</t>
+          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Idaho Power Company</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c327c9f4e800b849</t>
+          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Engineer, DevOps/Platform Reliability</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>PayCargo LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443de50c84ec577c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I - Large Language Models - AI &amp; Human Health Research</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf467b81837982e7</t>
+          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1c2968e4c859ad</t>
+          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6be32f39256627</t>
+          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps/Platform Reliability</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PayCargo LLC</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SNS, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d70c76f7b619354</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b0ec5a73d05efa</t>
+          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51215c06b0d02407</t>
+          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=888fa8c7756a9624</t>
+          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd33c14edf293d6</t>
+          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer- Generative AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95779ab6f886353b</t>
+          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1db80fe1bd8cd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Information Services Developer- Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4737707c3f640d35</t>
+          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Generative AI</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, MLOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547cee06d0bb3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138ef0c74c45d8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2109709d0fb65</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Information Services Developer- Databricks</t>
+          <t>Senior Analytic Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Oracle, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46d509d8362d109</t>
+          <t>https://www.indeed.com/viewjob?jk=e42d51f202bdd1cd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,77 +1956,77 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1777ba7f513541b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33cebafd850a30b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>ICT Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7144fb702e855f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - GCP services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9a6e5f3db9370</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ICT Data Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2029636ab554fae</t>
+          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d438cb8109fa60</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP services</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025b24fecbfea56e</t>
+          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Sr Engineer, BI - Onsite</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10db4f3f98dced0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer, Sportsbook Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,94 +2246,94 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c24ef6b14853f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Oracle, PostgreSQL, ETL, Power BI, Splunk, Docker</t>
+          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ff39b093bcf7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Engineer, BI - Onsite</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1698466286ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Sportsbook Platform</t>
+          <t>Database &amp; Data Platform Administrator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68bea5c8b6f32f3</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer (DBRE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a36241acc2482c</t>
+          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Data Ninjas Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8717662758adb1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Database &amp; Data Platform Administrator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>Sunsoft Services Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, ELT, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd1065a8aec697</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (DBRE)</t>
+          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac21e8c2033fca7</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Data Ninjas Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124e0eb6378e523b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0b9cecc2115912</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Life New Business Production Support (Java)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf50a63e39efffc</t>
+          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SEI Investments Developments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,139 +2621,139 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f4dff8bd114365</t>
+          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Platform Engineer, Azure / DevOps</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c5b2c44ca61f78</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst, Hardware &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEI Investments Developments</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, SQL Server, MongoDB, ETL, Tableau, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Snowflake, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd4d1666578a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c6767bdba48a7e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>MGR - SOFTWARE ENGINEERING</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9931af3931ffd36f</t>
+          <t>https://www.indeed.com/viewjob?jk=47845127b8be02d7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer, Azure / DevOps</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfa5ed5e8c3010c</t>
+          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Hardware &amp; Supply Chain</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Snowflake, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c6767bdba48a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=501ec28aee7919fd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18622e2ae9229fa</t>
+          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect, Dairy Predictive Solutions</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,50 +2901,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da1d5852709519d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Technical Architect, Dairy Predictive Solutions</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=60290cbd30568673</t>
         </is>
